--- a/data/huambocancha_alta.xlsx
+++ b/data/huambocancha_alta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,25 +462,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -508,7 +518,7 @@
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H2" t="n">
         <v>13</v>
@@ -517,9 +527,15 @@
         <v>9</v>
       </c>
       <c r="J2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -542,21 +558,27 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>12</v>
       </c>
-      <c r="I3" t="n">
-        <v>10</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
         <v>14</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -579,21 +601,27 @@
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
         <v>6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>14</v>
       </c>
       <c r="K4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -616,21 +644,27 @@
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
         <v>7</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>18</v>
       </c>
-      <c r="I5" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" t="n">
         <v>12</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -653,21 +687,27 @@
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="n">
         <v>7</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>16</v>
       </c>
-      <c r="I6" t="n">
-        <v>11</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>11</v>
       </c>
     </row>
@@ -690,16 +730,16 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
         <v>8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17</v>
-      </c>
-      <c r="I7" t="n">
-        <v>14</v>
       </c>
       <c r="J7" t="n">
         <v>17</v>
@@ -707,6 +747,12 @@
       <c r="K7" t="n">
         <v>14</v>
       </c>
+      <c r="L7" t="n">
+        <v>17</v>
+      </c>
+      <c r="M7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -727,7 +773,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -736,12 +782,18 @@
         <v>10</v>
       </c>
       <c r="I8" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
         <v>13</v>
       </c>
-      <c r="J8" t="n">
-        <v>11</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -764,21 +816,27 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
         <v>6</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>13</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>13</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>14</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -801,7 +859,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
@@ -813,9 +871,15 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" t="n">
         <v>14</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -838,21 +902,27 @@
         <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
         <v>8</v>
       </c>
-      <c r="H11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" t="n">
-        <v>11</v>
-      </c>
       <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11</v>
+      </c>
+      <c r="L11" t="n">
         <v>13</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -875,21 +945,27 @@
         <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
         <v>13</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -912,21 +988,27 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
         <v>7</v>
       </c>
-      <c r="H13" t="n">
-        <v>11</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9</v>
-      </c>
       <c r="J13" t="n">
+        <v>11</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="n">
         <v>14</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -949,21 +1031,27 @@
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
         <v>7</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>17</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>12</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>12</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -989,18 +1077,24 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" t="n">
         <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>17</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>25</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1015,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,25 +1145,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1108,7 +1212,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1123,10 +1227,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1156,30 +1270,36 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1211,28 +1331,42 @@
           <t>9</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1264,28 +1398,42 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1317,28 +1465,42 @@
           <t>9</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1370,28 +1532,42 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1423,7 +1599,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>10</t>
@@ -1436,15 +1616,25 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1476,28 +1666,42 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1529,7 +1733,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>10</t>
@@ -1547,10 +1755,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1582,28 +1800,42 @@
           <t>11</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1635,28 +1867,42 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1688,28 +1934,42 @@
           <t>6</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1741,28 +2001,42 @@
           <t>12</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1787,19 +2061,25 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>13</t>
         </is>

--- a/data/huambocancha_alta.xlsx
+++ b/data/huambocancha_alta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,25 +472,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -512,7 +522,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -524,18 +534,24 @@
         <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
         <v>9</v>
       </c>
       <c r="L2" t="n">
+        <v>13</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -567,18 +583,24 @@
         <v>16</v>
       </c>
       <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>12</v>
       </c>
-      <c r="K3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" t="n">
         <v>14</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -610,18 +632,24 @@
         <v>9</v>
       </c>
       <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
         <v>6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" t="n">
-        <v>10</v>
       </c>
       <c r="L4" t="n">
         <v>14</v>
       </c>
       <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -653,18 +681,24 @@
         <v>9</v>
       </c>
       <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>18</v>
       </c>
-      <c r="K5" t="n">
-        <v>11</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N5" t="n">
         <v>12</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -699,15 +733,21 @@
         <v>7</v>
       </c>
       <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
         <v>16</v>
       </c>
-      <c r="K6" t="n">
-        <v>11</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N6" t="n">
         <v>12</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>11</v>
       </c>
     </row>
@@ -739,13 +779,13 @@
         <v>10</v>
       </c>
       <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>17</v>
-      </c>
-      <c r="K7" t="n">
-        <v>14</v>
       </c>
       <c r="L7" t="n">
         <v>17</v>
@@ -753,6 +793,12 @@
       <c r="M7" t="n">
         <v>14</v>
       </c>
+      <c r="N7" t="n">
+        <v>17</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -788,12 +834,18 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
         <v>13</v>
       </c>
-      <c r="L8" t="n">
-        <v>11</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -825,18 +877,24 @@
         <v>11</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>13</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>13</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>14</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -871,15 +929,21 @@
         <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
         <v>10</v>
       </c>
       <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
         <v>14</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -911,18 +975,24 @@
         <v>10</v>
       </c>
       <c r="I11" t="n">
+        <v>11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="J11" t="n">
-        <v>10</v>
-      </c>
-      <c r="K11" t="n">
-        <v>11</v>
-      </c>
       <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
+        <v>11</v>
+      </c>
+      <c r="N11" t="n">
         <v>13</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -954,18 +1024,24 @@
         <v>10</v>
       </c>
       <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" t="n">
         <v>9</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
         <v>13</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -997,18 +1073,24 @@
         <v>10</v>
       </c>
       <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" t="n">
-        <v>11</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>11</v>
+      </c>
+      <c r="M13" t="n">
         <v>9</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1040,18 +1122,24 @@
         <v>10</v>
       </c>
       <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" t="n">
         <v>7</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>17</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>12</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>12</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1083,18 +1171,24 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>17</v>
+      </c>
+      <c r="J15" t="n">
         <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>17</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>17</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>25</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1109,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,25 +1249,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1202,7 +1306,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1222,25 +1326,35 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1281,25 +1395,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1348,25 +1472,35 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1415,25 +1549,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1487,20 +1631,30 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1549,25 +1703,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1626,15 +1786,25 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1683,25 +1853,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1755,7 +1935,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1765,10 +1945,20 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1817,25 +2007,35 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1884,25 +2084,35 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1949,27 +2159,29 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2018,25 +2230,35 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2067,19 +2289,25 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>13</t>
         </is>

--- a/data/huambocancha_alta.xlsx
+++ b/data/huambocancha_alta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,25 +482,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -540,18 +550,24 @@
         <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>9</v>
       </c>
       <c r="N2" t="n">
+        <v>13</v>
+      </c>
+      <c r="O2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -589,18 +605,24 @@
         <v>4</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>12</v>
       </c>
-      <c r="M3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P3" t="n">
         <v>14</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -638,18 +660,24 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>14</v>
-      </c>
-      <c r="M4" t="n">
-        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>14</v>
       </c>
       <c r="O4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -690,15 +718,21 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" t="n">
         <v>18</v>
       </c>
-      <c r="M5" t="n">
-        <v>11</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
+        <v>11</v>
+      </c>
+      <c r="P5" t="n">
         <v>12</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -736,18 +770,24 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>16</v>
       </c>
-      <c r="M6" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
+        <v>11</v>
+      </c>
+      <c r="P6" t="n">
         <v>12</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>11</v>
       </c>
     </row>
@@ -785,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>11</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>8</v>
-      </c>
-      <c r="L7" t="n">
-        <v>17</v>
-      </c>
-      <c r="M7" t="n">
-        <v>14</v>
       </c>
       <c r="N7" t="n">
         <v>17</v>
@@ -799,6 +839,12 @@
       <c r="O7" t="n">
         <v>14</v>
       </c>
+      <c r="P7" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -834,18 +880,24 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
         <v>13</v>
       </c>
-      <c r="N8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -883,18 +935,24 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>6</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>13</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>13</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>14</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -932,18 +990,24 @@
         <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>10</v>
       </c>
       <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
         <v>14</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -981,18 +1045,24 @@
         <v>10</v>
       </c>
       <c r="K11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" t="n">
-        <v>10</v>
-      </c>
-      <c r="M11" t="n">
-        <v>11</v>
-      </c>
       <c r="N11" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" t="n">
         <v>13</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1030,18 +1100,24 @@
         <v>8</v>
       </c>
       <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>9</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="M12" t="n">
-        <v>11</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
+        <v>11</v>
+      </c>
+      <c r="P12" t="n">
         <v>13</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1079,18 +1155,24 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
         <v>7</v>
       </c>
-      <c r="L13" t="n">
-        <v>11</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>11</v>
+      </c>
+      <c r="O13" t="n">
         <v>9</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>14</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1131,15 +1213,21 @@
         <v>7</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
         <v>17</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>12</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>12</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1177,18 +1265,24 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="n">
         <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>17</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>17</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>25</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1203,7 +1297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1259,25 +1353,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1336,25 +1440,31 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1403,27 +1513,29 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1482,25 +1594,31 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1562,22 +1680,28 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1636,25 +1760,31 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1709,25 +1839,31 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1786,25 +1922,31 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1863,25 +2005,31 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1940,14 +2088,10 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>10</t>
@@ -1955,10 +2099,20 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2017,25 +2171,31 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2094,25 +2254,31 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2163,25 +2329,35 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2243,22 +2419,28 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2295,19 +2477,25 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>13</t>
         </is>

--- a/data/huambocancha_alta.xlsx
+++ b/data/huambocancha_alta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,25 +492,30 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -553,21 +558,24 @@
         <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>9</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>13</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>9</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -608,21 +616,24 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>6</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>12</v>
       </c>
-      <c r="O3" t="n">
-        <v>10</v>
-      </c>
       <c r="P3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q3" t="n">
         <v>14</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -666,18 +677,21 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>6</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>14</v>
       </c>
-      <c r="O4" t="n">
-        <v>10</v>
-      </c>
       <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
         <v>14</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -718,21 +732,24 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>7</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>18</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>11</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>12</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -770,24 +787,27 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>7</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>16</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>11</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>12</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
     </row>
@@ -825,24 +845,27 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>8</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>17</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>14</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>17</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -886,20 +909,23 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>10</v>
       </c>
       <c r="O8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" t="n">
         <v>13</v>
-      </c>
-      <c r="P8" t="n">
-        <v>11</v>
       </c>
       <c r="Q8" t="n">
         <v>11</v>
       </c>
+      <c r="R8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -941,18 +967,21 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
         <v>6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>13</v>
       </c>
       <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
         <v>14</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -993,10 +1022,10 @@
         <v>6</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>10</v>
@@ -1005,9 +1034,12 @@
         <v>10</v>
       </c>
       <c r="P10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q10" t="n">
         <v>14</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1048,21 +1080,24 @@
         <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>8</v>
       </c>
-      <c r="N11" t="n">
-        <v>10</v>
-      </c>
       <c r="O11" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" t="n">
         <v>11</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>13</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1103,21 +1138,24 @@
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>9</v>
       </c>
       <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
         <v>11</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>13</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1161,18 +1199,21 @@
         <v>3</v>
       </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>7</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>11</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>9</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>14</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1213,21 +1254,24 @@
         <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>7</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>17</v>
-      </c>
-      <c r="O14" t="n">
-        <v>12</v>
       </c>
       <c r="P14" t="n">
         <v>12</v>
       </c>
       <c r="Q14" t="n">
+        <v>12</v>
+      </c>
+      <c r="R14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1274,15 +1318,18 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>17</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>25</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1297,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1363,25 +1410,30 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1443,28 +1495,33 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1514,28 +1571,33 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1598,27 +1660,28 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1680,28 +1743,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1760,31 +1828,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1839,31 +1908,36 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1926,11 +2000,7 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>10</t>
@@ -1938,15 +2008,20 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2011,25 +2086,30 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2091,12 +2171,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>10</t>
@@ -2109,10 +2189,15 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2174,28 +2259,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2257,28 +2347,33 @@
           <t>6</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2337,27 +2432,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2419,28 +2515,33 @@
           <t>7</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2484,18 +2585,19 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>13</t>
         </is>

--- a/data/huambocancha_alta.xlsx
+++ b/data/huambocancha_alta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,25 +497,40 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -564,18 +579,27 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O2" t="n">
+        <v>11</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>9</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>13</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>9</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -619,21 +643,30 @@
         <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>6</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>12</v>
       </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="n">
         <v>14</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -677,21 +710,30 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>6</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>14</v>
       </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="n">
         <v>14</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -735,21 +777,30 @@
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>7</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>18</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>11</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>12</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -793,21 +844,30 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>7</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>16</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>11</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>12</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>11</v>
       </c>
     </row>
@@ -845,27 +905,36 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>8</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>17</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>14</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>17</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -909,21 +978,30 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10</v>
+      </c>
+      <c r="R8" t="n">
+        <v>10</v>
+      </c>
+      <c r="S8" t="n">
         <v>13</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -967,21 +1045,30 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>13</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>13</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>14</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1025,21 +1112,30 @@
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
         <v>14</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1083,21 +1179,30 @@
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>8</v>
       </c>
-      <c r="O11" t="n">
-        <v>10</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="n">
         <v>11</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>13</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1141,21 +1246,30 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>9</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>9</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>11</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>13</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1199,21 +1313,30 @@
         <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>7</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>11</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>9</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>14</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1257,21 +1380,30 @@
         <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>7</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>17</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>12</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>12</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1315,21 +1447,30 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>17</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>25</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1344,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,25 +1556,40 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1503,25 +1659,36 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1576,28 +1743,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1660,28 +1842,43 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1748,28 +1945,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1832,28 +2044,43 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1908,7 +2135,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1916,28 +2143,39 @@
           <t>5</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2000,28 +2238,43 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2086,30 +2339,41 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2176,28 +2440,43 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2264,28 +2543,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2352,28 +2646,43 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2432,28 +2741,43 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2520,28 +2844,43 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2584,20 +2923,35 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>13</t>
         </is>

--- a/data/huambocancha_alta.xlsx
+++ b/data/huambocancha_alta.xlsx
@@ -585,7 +585,7 @@
         <v>11</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
         <v>9</v>
@@ -719,13 +719,13 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
         <v>7</v>
@@ -853,7 +853,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>7</v>
@@ -920,7 +920,7 @@
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
         <v>8</v>
@@ -987,7 +987,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>10</v>
@@ -1054,7 +1054,7 @@
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
         <v>6</v>
@@ -1121,7 +1121,7 @@
         <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
         <v>8</v>
@@ -1255,7 +1255,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>9</v>
@@ -1389,7 +1389,7 @@
         <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
         <v>7</v>
@@ -1456,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1667,7 +1667,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
@@ -1857,7 +1861,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>6</t>
@@ -1865,7 +1873,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1960,7 +1968,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>7</t>
@@ -2059,7 +2071,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>7</t>
@@ -2154,7 +2170,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>8</t>
@@ -2253,7 +2273,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>10</t>
@@ -2352,7 +2376,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>6</t>
@@ -2455,7 +2483,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>10</t>
@@ -2558,7 +2590,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>8</t>
@@ -2661,7 +2697,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>9</t>
@@ -2859,7 +2899,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>7</t>
@@ -2936,7 +2980,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>

--- a/data/huambocancha_alta.xlsx
+++ b/data/huambocancha_alta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,25 +512,30 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -588,18 +593,21 @@
         <v>5</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>13</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>9</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>21</v>
       </c>
     </row>
@@ -655,18 +663,21 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
         <v>6</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>12</v>
       </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
       <c r="T3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U3" t="n">
         <v>14</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -722,18 +733,21 @@
         <v>3</v>
       </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>13</v>
       </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
       <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="n">
         <v>14</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -789,18 +803,21 @@
         <v>4</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>7</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>18</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>11</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>12</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>13</v>
       </c>
     </row>
@@ -856,18 +873,21 @@
         <v>4</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>7</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>12</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>11</v>
       </c>
     </row>
@@ -923,18 +943,21 @@
         <v>6</v>
       </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>8</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>17</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>14</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>17</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -990,18 +1013,21 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>10</v>
       </c>
       <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="n">
         <v>13</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1057,18 +1083,21 @@
         <v>5</v>
       </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>13</v>
       </c>
       <c r="S9" t="n">
         <v>13</v>
       </c>
       <c r="T9" t="n">
+        <v>13</v>
+      </c>
+      <c r="U9" t="n">
         <v>14</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1124,7 +1153,7 @@
         <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>10</v>
@@ -1133,9 +1162,12 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
         <v>14</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1191,18 +1223,21 @@
         <v>6</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>8</v>
       </c>
-      <c r="R11" t="n">
-        <v>10</v>
-      </c>
       <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="n">
         <v>11</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>13</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1258,18 +1293,21 @@
         <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>9</v>
       </c>
       <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="n">
         <v>11</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>13</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1325,18 +1363,21 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
         <v>7</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>11</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>9</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>14</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1392,18 +1433,21 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>7</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>17</v>
-      </c>
-      <c r="S14" t="n">
-        <v>12</v>
       </c>
       <c r="T14" t="n">
         <v>12</v>
       </c>
       <c r="U14" t="n">
+        <v>12</v>
+      </c>
+      <c r="V14" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1462,15 +1506,18 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>17</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>25</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -1485,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,25 +1618,30 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1672,27 +1724,28 @@
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1765,25 +1818,30 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1866,27 +1924,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1973,27 +2032,28 @@
           <t>4</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2076,27 +2136,28 @@
           <t>4</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2175,27 +2236,28 @@
           <t>6</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2278,11 +2340,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>10</t>
@@ -2290,15 +2348,20 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2381,27 +2444,28 @@
           <t>5</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -2488,11 +2552,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>10</t>
@@ -2505,10 +2565,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -2595,27 +2660,28 @@
           <t>6</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -2702,27 +2768,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2799,25 +2866,30 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -2904,27 +2976,28 @@
           <t>3</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -2984,18 +3057,19 @@
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
